--- a/backend/data/financials_by_company/002137.SZ.xlsx
+++ b/backend/data/financials_by_company/002137.SZ.xlsx
@@ -3897,192 +3897,192 @@
       </c>
       <c r="DD1" t="inlineStr">
         <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>prevName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>nameChangeDate</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>prevName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>nameChangeDate</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -4094,7 +4094,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shiyida Jinlong Factory</t>
+          <t>No. 1 Shiyida Jinlong Factory Area</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>518116</t>
+          <t>518118</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Shenzhen Sea Star Technology Co.,Ltd, together with its subsidiaries, engages in the intelligent hardware manufacturing, research and development, production and sales of intelligent terminal products in China. The company offers semiconductor packaging and testing equipment components; and new energy products, such as inverters, automotive electronics, and other related products. It also engaged in the design, development, production and sales of LED smart lighting and related supporting smart terminal products, as well as provides LED solutions. The company was formerly known as Shen Zhen Mindata Holding Co., Ltd and changed its name to Shenzhen Sea Star Technology Co.,Ltd in March 2021. Shenzhen Sea Star Technology Co.,Ltd was founded in 1998 and is headquartered in Shenzhen, China.</t>
+          <t>Shenzhen Sea Star Technology Co.,Ltd, together with its subsidiaries, engages in the smart hardware manufacturing, research and development, production, and sales of smart terminal products in China. The company offers engineering testing, manufacturing, and supply chain management services for industrial-grade equipment and related products; semiconductor packaging equipment components, automotive electronics, and other services. It also engaged in the design, research and development, production and sales of LED smart lighting and related supporting smart terminal products, as well as provides LED solutions. The company was formerly known as Shen Zhen Mindata Holding Co., Ltd and changed its name to Shenzhen Sea Star Technology Co.,Ltd in March 2021. Shenzhen Sea Star Technology Co.,Ltd was founded in 1998 and is headquartered in Shenzhen, China.</t>
         </is>
       </c>
       <c r="N2" t="n">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Yamei  Chen', 'age': 50, 'title': 'Founder &amp; Chairman', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xin  Qiao', 'age': 62, 'title': 'Founder, Director &amp; CEO', 'yearBorn': 1963, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jie Heng  Pan', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Ms. Yamei  Chen', 'age': 50, 'title': 'Founder &amp; Chairman', 'yearBorn': 1975, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xin  Qiao', 'age': 62, 'title': 'Founder, Director &amp; CEO', 'yearBorn': 1963, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Suhua  Yuan', 'age': 46, 'title': 'Secretary of the Board of Directors', 'yearBorn': 1979, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jie Heng  Pan', 'title': 'Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4177,34 +4177,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>10.55</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>10.34</v>
+        <v>10.36</v>
       </c>
       <c r="U2" t="n">
-        <v>10.48</v>
+        <v>9.93</v>
       </c>
       <c r="V2" t="n">
-        <v>11.09</v>
+        <v>10.88</v>
       </c>
       <c r="W2" t="n">
-        <v>10.55</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>10.34</v>
+        <v>10.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.48</v>
+        <v>9.93</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.09</v>
+        <v>10.88</v>
       </c>
       <c r="AA2" t="n">
         <v>0.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.46</v>
+        <v>0.48</v>
       </c>
       <c r="AC2" t="n">
         <v>1779753600</v>
@@ -4213,31 +4213,31 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.605</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AF2" t="n">
-        <v>156.42857</v>
+        <v>130.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>91924021</v>
+        <v>76592111</v>
       </c>
       <c r="AH2" t="n">
-        <v>91924021</v>
+        <v>76592111</v>
       </c>
       <c r="AI2" t="n">
-        <v>30239244</v>
+        <v>39745539</v>
       </c>
       <c r="AJ2" t="n">
-        <v>88881606</v>
+        <v>77864997</v>
       </c>
       <c r="AK2" t="n">
-        <v>88881606</v>
+        <v>77864997</v>
       </c>
       <c r="AL2" t="n">
-        <v>10.95</v>
+        <v>10.4</v>
       </c>
       <c r="AM2" t="n">
-        <v>10.96</v>
+        <v>10.41</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4246,10 +4246,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>6323677696</v>
+        <v>6017600512</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6092676209</v>
+        <v>6219727277</v>
       </c>
       <c r="AR2" t="n">
         <v>7.72</v>
@@ -4264,19 +4264,19 @@
         <v>1.68566</v>
       </c>
       <c r="AV2" t="n">
-        <v>8.836574000000001</v>
+        <v>8.408868</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.897399999999999</v>
+        <v>9.337400000000001</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.876749999999999</v>
+        <v>8.9597</v>
       </c>
       <c r="AY2" t="n">
         <v>0.05</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.0047393367</v>
+        <v>0.0050556115</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -4287,7 +4287,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>6257138176</v>
+        <v>5779889152</v>
       </c>
       <c r="BD2" t="n">
         <v>0.060399998</v>
@@ -4299,10 +4299,10 @@
         <v>577504854</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.4525</v>
+        <v>0.45001</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.01748</v>
+        <v>0.0149300005</v>
       </c>
       <c r="BI2" t="n">
         <v>577504854</v>
@@ -4311,7 +4311,7 @@
         <v>2.662</v>
       </c>
       <c r="BK2" t="n">
-        <v>4.1134486</v>
+        <v>3.9143503</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4329,7 +4329,7 @@
         <v>43221304</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -4340,16 +4340,16 @@
         <v>1367798400</v>
       </c>
       <c r="BT2" t="n">
-        <v>8.744</v>
+        <v>8.077</v>
       </c>
       <c r="BU2" t="n">
-        <v>94.709</v>
+        <v>87.486</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.23971796</v>
+        <v>0.16903079</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.24487448</v>
+        <v>0.20116603</v>
       </c>
       <c r="BX2" t="n">
         <v>0.05</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="CA2" t="n">
-        <v>10.95</v>
+        <v>10.42</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>147994496</v>
+        <v>319165952</v>
       </c>
       <c r="CD2" t="n">
-        <v>0.256</v>
+        <v>0.553</v>
       </c>
       <c r="CE2" t="n">
         <v>66066672</v>
@@ -4383,7 +4383,7 @@
         <v>8296452</v>
       </c>
       <c r="CG2" t="n">
-        <v>1.195</v>
+        <v>1.74</v>
       </c>
       <c r="CH2" t="n">
         <v>2.247</v>
@@ -4407,7 +4407,7 @@
         <v>126662744</v>
       </c>
       <c r="CO2" t="n">
-        <v>87868728</v>
+        <v>259040208</v>
       </c>
       <c r="CP2" t="n">
         <v>70812384</v>
@@ -4465,147 +4465,147 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DD2" t="b">
+      <c r="DD2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Shen Zhen Mindata Holding Co., Ltd</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="DH2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="n">
+      <c r="DI2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1.0825996</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0.11594229</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>1.4603004</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.16298543</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>SHENZHEN SEA STAR TECHNOLOGY CO</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>Shenzhen Sea Star Technology Co.,Ltd</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>0.52999973</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>9.93 - 10.88</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>39745539</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>2.7000003</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.34974098</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>7.72 - 11.87</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-1.4499998</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.12215668</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>16.903078</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1619521140</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>1619521140</v>
+      </c>
+      <c r="EB2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EC2" t="n">
         <v>1181698200000</v>
       </c>
-      <c r="DF2" t="n">
-        <v>3.7914655</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="DH2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DI2" t="n">
-        <v>1782111843</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EF2" t="n">
+        <v>1783062261</v>
+      </c>
+      <c r="EG2" t="inlineStr">
         <is>
           <t>SHZ</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>finmb_34556603</t>
         </is>
       </c>
-      <c r="DL2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>Asia/Shanghai</t>
         </is>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="EJ2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DN2" t="n">
+      <c r="EK2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DO2" t="inlineStr">
+      <c r="EL2" t="inlineStr">
         <is>
           <t>cn_market</t>
         </is>
       </c>
-      <c r="DP2" t="b">
+      <c r="EM2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>SHENZHEN SEA STAR TECHNOLOGY CO</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>Shenzhen Sea Star Technology Co.,Ltd</t>
-        </is>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.39999962</v>
-      </c>
-      <c r="DU2" t="inlineStr">
-        <is>
-          <t>10.48 - 11.09</t>
-        </is>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>30239244</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.4183938</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>7.72 - 11.87</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.9200001</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.077506326</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>23.971796</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>1619521140</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>2.0526</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.2306966</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>2.0732498</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>0.23355956</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>Shen Zhen Mindata Holding Co., Ltd</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="EO2" t="b">
-        <v>0</v>
+      <c r="EN2" t="n">
+        <v>5.3589454</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>10.42</v>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
